--- a/base_contagem_semanal.xlsx
+++ b/base_contagem_semanal.xlsx
@@ -270,7 +270,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/1nbGc_0d3nWny9uMX_R4zOmKkzxWUNp-pBxvfbr7lqFM/edit?gid=1385808625#gid=1385808625"",""Contagem!A2:T"")"),"EST")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""https://docs.google.com/spreadsheets/d/15-t0ohJM1pWQpK6y9PcraAhFg4D9ywS-v_JG9CNmywA/edit?gid=1385808625#gid=1385808625"",""Contagem!A2:T"")"),"EST")</f>
         <v>EST</v>
       </c>
       <c r="B1" s="1" t="str">
@@ -338,14 +338,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -372,8 +366,8 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="K2" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -381,8 +375,8 @@
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="2" t="str">
@@ -390,8 +384,8 @@
         <v/>
       </c>
       <c r="P2" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -402,14 +396,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B3" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -434,13 +422,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K3" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -448,8 +433,8 @@
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),56.0)</f>
+        <v>56</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="2" t="str">
@@ -457,8 +442,8 @@
         <v/>
       </c>
       <c r="P3" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -469,14 +454,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B4" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -501,13 +480,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="K4" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -515,8 +491,8 @@
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
-        <v>21</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="2" t="str">
@@ -524,8 +500,8 @@
         <v/>
       </c>
       <c r="P4" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -536,14 +512,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B5" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -568,13 +538,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
       <c r="K5" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -582,8 +549,8 @@
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),41.0)</f>
-        <v>41</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),128.0)</f>
+        <v>128</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="2" t="str">
@@ -591,8 +558,8 @@
         <v/>
       </c>
       <c r="P5" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
+        <v>11</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -603,14 +570,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B6" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -635,13 +596,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -649,8 +607,8 @@
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="2" t="str">
@@ -658,8 +616,8 @@
         <v/>
       </c>
       <c r="P6" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -670,14 +628,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B7" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -702,13 +654,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -716,8 +665,8 @@
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="2" t="str">
@@ -725,8 +674,8 @@
         <v/>
       </c>
       <c r="P7" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
@@ -737,14 +686,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B8" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -769,13 +712,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I8" s="1"/>
       <c r="J8" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="K8" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -783,8 +723,8 @@
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.4906)</f>
-        <v>10.4906</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.7398)</f>
+        <v>24.7398</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="2" t="str">
@@ -792,8 +732,8 @@
         <v/>
       </c>
       <c r="P8" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
@@ -804,14 +744,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B9" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
       <c r="C9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -836,10 +770,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
         <v>7</v>
@@ -850,8 +781,8 @@
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.84)</f>
-        <v>1.84</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.625)</f>
+        <v>1.625</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="2" t="str">
@@ -871,14 +802,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -903,13 +828,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I10" s="1"/>
       <c r="J10" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="K10" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -917,8 +839,8 @@
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.34)</f>
+        <v>1.34</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="2" t="str">
@@ -926,8 +848,8 @@
         <v/>
       </c>
       <c r="P10" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -938,14 +860,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B11" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
       <c r="C11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -970,13 +886,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I11" s="1"/>
       <c r="J11" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K11" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -984,8 +897,8 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.31)</f>
-        <v>0.31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.505)</f>
+        <v>0.505</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="2" t="str">
@@ -993,8 +906,8 @@
         <v/>
       </c>
       <c r="P11" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1005,14 +918,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B12" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
       <c r="C12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1037,13 +944,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I12" s="1"/>
       <c r="J12" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="K12" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1051,8 +955,8 @@
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.415)</f>
-        <v>0.415</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.33)</f>
+        <v>0.33</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="2" t="str">
@@ -1060,8 +964,8 @@
         <v/>
       </c>
       <c r="P12" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1072,14 +976,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B13" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
       <c r="C13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1104,22 +1002,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I13" s="1"/>
       <c r="J13" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="K13" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L13" s="1"/>
-      <c r="M13" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+      <c r="M13" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.135)</f>
+        <v>0.135</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="2" t="str">
@@ -1127,8 +1022,8 @@
         <v/>
       </c>
       <c r="P13" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1139,14 +1034,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
       <c r="C14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1168,13 +1057,10 @@
         <v>12</v>
       </c>
       <c r="H14" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
-      </c>
-      <c r="I14" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="1"/>
       <c r="J14" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1194,8 +1080,8 @@
         <v/>
       </c>
       <c r="P14" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-24.0)</f>
-        <v>-24</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -1206,14 +1092,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
-      <c r="B15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
       <c r="C15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1235,16 +1115,13 @@
         <v>0.9</v>
       </c>
       <c r="H15" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
-      </c>
-      <c r="I15" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="1"/>
       <c r="J15" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="K15" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -1252,8 +1129,8 @@
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.435)</f>
-        <v>1.435</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.877)</f>
+        <v>3.877</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="2" t="str">
@@ -1261,8 +1138,8 @@
         <v/>
       </c>
       <c r="P15" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-6.0)</f>
-        <v>-6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -1273,14 +1150,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
-      <c r="B16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
       <c r="C16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1302,25 +1173,22 @@
         <v>1</v>
       </c>
       <c r="H16" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
-      </c>
-      <c r="I16" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="1"/>
       <c r="J16" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="K16" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.94)</f>
-        <v>6.94</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.86)</f>
+        <v>7.86</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="2" t="str">
@@ -1328,8 +1196,8 @@
         <v/>
       </c>
       <c r="P16" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -1340,14 +1208,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B17" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
       <c r="C17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1369,13 +1231,10 @@
         <v>100</v>
       </c>
       <c r="H17" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I17" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="1"/>
       <c r="J17" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1386,8 +1245,8 @@
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.042)</f>
-        <v>0.042</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.126)</f>
+        <v>0.126</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="2" t="str">
@@ -1395,8 +1254,8 @@
         <v/>
       </c>
       <c r="P17" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -1407,14 +1266,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B18" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
       <c r="C18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1436,13 +1289,10 @@
         <v>50</v>
       </c>
       <c r="H18" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I18" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="1"/>
       <c r="J18" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1462,8 +1312,8 @@
         <v/>
       </c>
       <c r="P18" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1474,14 +1324,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B19" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
       <c r="C19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1503,13 +1347,10 @@
         <v>50</v>
       </c>
       <c r="H19" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I19" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="1"/>
       <c r="J19" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1529,8 +1370,8 @@
         <v/>
       </c>
       <c r="P19" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -1541,14 +1382,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B20" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
       <c r="C20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1570,13 +1405,10 @@
         <v>50</v>
       </c>
       <c r="H20" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I20" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="1"/>
       <c r="J20" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1596,8 +1428,8 @@
         <v/>
       </c>
       <c r="P20" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -1608,14 +1440,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B21" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
       <c r="C21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1637,13 +1463,10 @@
         <v>50</v>
       </c>
       <c r="H21" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I21" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="1"/>
       <c r="J21" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1663,8 +1486,8 @@
         <v/>
       </c>
       <c r="P21" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -1675,14 +1498,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B22" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
       <c r="C22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1704,13 +1521,10 @@
         <v>50</v>
       </c>
       <c r="H22" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I22" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1"/>
       <c r="J22" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1730,8 +1544,8 @@
         <v/>
       </c>
       <c r="P22" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -1742,14 +1556,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B23" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1771,13 +1579,10 @@
         <v>50</v>
       </c>
       <c r="H23" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I23" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="1"/>
       <c r="J23" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1797,8 +1602,8 @@
         <v/>
       </c>
       <c r="P23" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -1809,14 +1614,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
       <c r="C24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1838,13 +1637,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I24" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="1"/>
       <c r="J24" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1864,8 +1660,8 @@
         <v/>
       </c>
       <c r="P24" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -1876,14 +1672,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B25" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
       <c r="C25" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1905,13 +1695,10 @@
         <v>2400</v>
       </c>
       <c r="H25" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I25" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="1"/>
       <c r="J25" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -1931,8 +1718,8 @@
         <v/>
       </c>
       <c r="P25" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -1943,14 +1730,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B26" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -1972,13 +1753,10 @@
         <v>100</v>
       </c>
       <c r="H26" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I26" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1"/>
       <c r="J26" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -1989,8 +1767,8 @@
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
-        <v>76</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),131.0)</f>
+        <v>131</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="2" t="str">
@@ -1998,8 +1776,8 @@
         <v/>
       </c>
       <c r="P26" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
@@ -2010,14 +1788,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B27" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
       <c r="C27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2039,20 +1811,17 @@
         <v>500</v>
       </c>
       <c r="H27" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I27" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1"/>
       <c r="J27" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K27" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="3" t="str">
@@ -2065,8 +1834,8 @@
         <v/>
       </c>
       <c r="P27" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -2077,14 +1846,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B28" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
       <c r="C28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2106,13 +1869,10 @@
         <v>500</v>
       </c>
       <c r="H28" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I28" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="1"/>
       <c r="J28" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2132,8 +1892,8 @@
         <v/>
       </c>
       <c r="P28" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
@@ -2144,14 +1904,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B29" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2173,13 +1927,10 @@
         <v>100</v>
       </c>
       <c r="H29" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I29" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="1"/>
       <c r="J29" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2199,8 +1950,8 @@
         <v/>
       </c>
       <c r="P29" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -2211,14 +1962,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B30" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
       <c r="C30" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2240,13 +1985,10 @@
         <v>500</v>
       </c>
       <c r="H30" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I30" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="1"/>
       <c r="J30" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2266,8 +2008,8 @@
         <v/>
       </c>
       <c r="P30" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
@@ -2278,14 +2020,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
       <c r="C31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2307,13 +2043,10 @@
         <v>100</v>
       </c>
       <c r="H31" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I31" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="1"/>
       <c r="J31" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2333,8 +2066,8 @@
         <v/>
       </c>
       <c r="P31" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
@@ -2345,14 +2078,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B32" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
       <c r="C32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2374,13 +2101,10 @@
         <v>1</v>
       </c>
       <c r="H32" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I32" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="1"/>
       <c r="J32" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2400,8 +2124,8 @@
         <v/>
       </c>
       <c r="P32" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
@@ -2412,14 +2136,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B33" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2441,25 +2159,22 @@
         <v>0.51</v>
       </c>
       <c r="H33" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I33" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="1"/>
       <c r="J33" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
       <c r="K33" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.46)</f>
-        <v>0.46</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.56)</f>
+        <v>0.56</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="2" t="str">
@@ -2467,8 +2182,8 @@
         <v/>
       </c>
       <c r="P33" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -2479,14 +2194,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B34" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2508,13 +2217,10 @@
         <v>1</v>
       </c>
       <c r="H34" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I34" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="1"/>
       <c r="J34" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2534,8 +2240,8 @@
         <v/>
       </c>
       <c r="P34" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
@@ -2546,14 +2252,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B35" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
       <c r="C35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2575,13 +2275,10 @@
         <v>1</v>
       </c>
       <c r="H35" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I35" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="1"/>
       <c r="J35" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2601,8 +2298,8 @@
         <v/>
       </c>
       <c r="P35" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -2613,14 +2310,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B36" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
       <c r="C36" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -2642,25 +2333,22 @@
         <v>24</v>
       </c>
       <c r="H36" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="I36" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
       <c r="K36" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.0)</f>
+        <v>55</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="2" t="str">
@@ -2668,8 +2356,8 @@
         <v/>
       </c>
       <c r="P36" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -2680,17 +2368,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B37" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -2709,25 +2391,22 @@
         <v>24</v>
       </c>
       <c r="H37" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="I37" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
       <c r="K37" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),34.0)</f>
+        <v>34</v>
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="2" t="str">
@@ -2735,8 +2414,8 @@
         <v/>
       </c>
       <c r="P37" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -2747,17 +2426,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B38" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -2779,13 +2452,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I38" s="1"/>
       <c r="J38" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="K38" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2793,8 +2463,8 @@
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="2" t="str">
@@ -2802,8 +2472,8 @@
         <v/>
       </c>
       <c r="P38" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
@@ -2814,17 +2484,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B39" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D39" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -2846,10 +2510,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I39" s="1"/>
       <c r="J39" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2860,8 +2521,8 @@
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="2" t="str">
@@ -2881,17 +2542,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B40" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="C40" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -2910,16 +2565,13 @@
         <v>24</v>
       </c>
       <c r="H40" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="I40" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="1"/>
       <c r="J40" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K40" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2927,8 +2579,8 @@
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
-        <v>22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="2" t="str">
@@ -2936,8 +2588,8 @@
         <v/>
       </c>
       <c r="P40" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
@@ -2948,17 +2600,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B41" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C41" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -2977,16 +2623,13 @@
         <v>24</v>
       </c>
       <c r="H41" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I41" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="1"/>
       <c r="J41" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="K41" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2994,8 +2637,8 @@
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),28.0)</f>
-        <v>28</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
+        <v>78</v>
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="2" t="str">
@@ -3003,8 +2646,8 @@
         <v/>
       </c>
       <c r="P41" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
@@ -3015,14 +2658,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="B42" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3044,25 +2681,22 @@
         <v>1</v>
       </c>
       <c r="H42" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I42" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="1"/>
       <c r="J42" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="K42" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),48.0)</f>
-        <v>48</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),109.0)</f>
+        <v>109</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="2" t="str">
@@ -3070,8 +2704,8 @@
         <v/>
       </c>
       <c r="P42" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="2">
@@ -3085,14 +2719,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B43" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
       <c r="C43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3114,16 +2742,13 @@
         <v>1</v>
       </c>
       <c r="H43" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="I43" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="1"/>
       <c r="J43" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="K43" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3131,8 +2756,8 @@
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45.0)</f>
+        <v>45</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="2" t="str">
@@ -3140,8 +2765,8 @@
         <v/>
       </c>
       <c r="P43" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="2">
@@ -3155,14 +2780,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B44" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
       <c r="C44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3184,25 +2803,22 @@
         <v>1</v>
       </c>
       <c r="H44" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="I44" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
       <c r="K44" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),54.0)</f>
+        <v>54</v>
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="2" t="str">
@@ -3210,8 +2826,8 @@
         <v/>
       </c>
       <c r="P44" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="2">
@@ -3225,14 +2841,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B45" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
       <c r="C45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3254,16 +2864,13 @@
         <v>1</v>
       </c>
       <c r="H45" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
-      <c r="I45" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="1"/>
       <c r="J45" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="K45" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -3271,8 +2878,8 @@
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
-        <v>14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="2" t="str">
@@ -3280,8 +2887,8 @@
         <v/>
       </c>
       <c r="P45" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-6.0)</f>
-        <v>-6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="2">
@@ -3295,14 +2902,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B46" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
       <c r="C46" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3324,13 +2925,10 @@
         <v>1</v>
       </c>
       <c r="H46" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I46" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="1"/>
       <c r="J46" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -3341,8 +2939,8 @@
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="2" t="str">
@@ -3350,8 +2948,8 @@
         <v/>
       </c>
       <c r="P46" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q46" s="1"/>
       <c r="R46" s="2">
@@ -3365,14 +2963,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B47" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
       <c r="C47" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3394,13 +2986,10 @@
         <v>1</v>
       </c>
       <c r="H47" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I47" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="1"/>
       <c r="J47" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -3411,8 +3000,8 @@
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="N47" s="1"/>
       <c r="O47" s="2" t="str">
@@ -3420,8 +3009,8 @@
         <v/>
       </c>
       <c r="P47" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="2">
@@ -3435,14 +3024,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B48" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
       <c r="C48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3464,25 +3047,22 @@
         <v>1</v>
       </c>
       <c r="H48" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="I48" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
       <c r="K48" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L48" s="1"/>
       <c r="M48" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="2" t="str">
@@ -3490,8 +3070,8 @@
         <v/>
       </c>
       <c r="P48" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q48" s="1"/>
       <c r="R48" s="2">
@@ -3505,17 +3085,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B49" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C49" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -3537,17 +3111,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I49" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="I49" s="1"/>
       <c r="J49" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K49" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="3">
@@ -3572,17 +3143,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B50" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EMPORIO DAS TORTAS")</f>
@@ -3601,20 +3166,17 @@
         <v>24</v>
       </c>
       <c r="H50" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I50" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="1"/>
       <c r="J50" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
       <c r="K50" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="3">
@@ -3627,8 +3189,8 @@
         <v/>
       </c>
       <c r="P50" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
@@ -3639,14 +3201,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B51" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
       <c r="C51" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3668,25 +3224,22 @@
         <v>1</v>
       </c>
       <c r="H51" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="I51" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="J51" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
       <c r="K51" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
+        <v>26</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="2" t="str">
@@ -3694,8 +3247,8 @@
         <v/>
       </c>
       <c r="P51" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q51" s="1"/>
       <c r="R51" s="2">
@@ -3709,14 +3262,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B52" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
       <c r="C52" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3738,25 +3285,22 @@
         <v>1</v>
       </c>
       <c r="H52" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I52" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="1"/>
       <c r="J52" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K52" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L52" s="1"/>
-      <c r="M52" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+      <c r="M52" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
+        <v/>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="2" t="str">
@@ -3764,8 +3308,8 @@
         <v/>
       </c>
       <c r="P52" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q52" s="1"/>
       <c r="R52" s="2">
@@ -3779,14 +3323,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B53" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
       <c r="C53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3808,25 +3346,22 @@
         <v>1</v>
       </c>
       <c r="H53" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I53" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="1"/>
       <c r="J53" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K53" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L53" s="1"/>
-      <c r="M53" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
+      <c r="M53" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
+        <v/>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="2" t="str">
@@ -3834,8 +3369,8 @@
         <v/>
       </c>
       <c r="P53" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="2">
@@ -3849,15 +3384,12 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B54" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C54" s="1"/>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"POMELO - MIN. 550,00 PEDIR SEGUNDA (RIBEIRO)")</f>
         <v>POMELO - MIN. 550,00 PEDIR SEGUNDA (RIBEIRO)</v>
@@ -3875,25 +3407,22 @@
         <v>84</v>
       </c>
       <c r="H54" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I54" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="1"/>
       <c r="J54" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K54" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),98.0)</f>
-        <v>98</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),170.0)</f>
+        <v>170</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="2" t="str">
@@ -3901,8 +3430,8 @@
         <v/>
       </c>
       <c r="P54" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
@@ -3913,14 +3442,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B55" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
       <c r="C55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -3942,25 +3465,22 @@
         <v>50</v>
       </c>
       <c r="H55" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I55" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="1"/>
       <c r="J55" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
       <c r="K55" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L55" s="1"/>
       <c r="M55" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),31.5)</f>
-        <v>31.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.5)</f>
+        <v>73.5</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="2" t="str">
@@ -3968,8 +3488,8 @@
         <v/>
       </c>
       <c r="P55" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
@@ -3980,17 +3500,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B56" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C56" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
-        <v>49</v>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"POMELO - MIN. 550,00 PEDIR SEGUNDA (RIBEIRO)")</f>
@@ -4012,10 +3526,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I56" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I56" s="1"/>
       <c r="J56" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -4026,8 +3537,8 @@
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
+        <v>23</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="2" t="str">
@@ -4047,14 +3558,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B57" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
       <c r="C57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4076,16 +3581,13 @@
         <v>1</v>
       </c>
       <c r="H57" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
-        <v>24</v>
-      </c>
-      <c r="I57" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="1"/>
       <c r="J57" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="K57" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4093,8 +3595,8 @@
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="2" t="str">
@@ -4102,8 +3604,8 @@
         <v/>
       </c>
       <c r="P57" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-22.0)</f>
-        <v>-22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
+        <v>10</v>
       </c>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
@@ -4114,14 +3616,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B58" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
       <c r="C58" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4143,16 +3639,13 @@
         <v>1</v>
       </c>
       <c r="H58" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
-      </c>
-      <c r="I58" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="1"/>
       <c r="J58" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="K58" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4160,8 +3653,8 @@
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="2" t="str">
@@ -4169,8 +3662,8 @@
         <v/>
       </c>
       <c r="P58" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-7.0)</f>
-        <v>-7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),27.0)</f>
+        <v>27</v>
       </c>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
@@ -4181,14 +3674,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B59" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
       <c r="C59" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4210,25 +3697,22 @@
         <v>1</v>
       </c>
       <c r="H59" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
         <v>20</v>
       </c>
-      <c r="I59" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J59" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
       <c r="K59" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L59" s="1"/>
-      <c r="M59" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
+      <c r="M59" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="2" t="str">
@@ -4236,8 +3720,8 @@
         <v/>
       </c>
       <c r="P59" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-20.0)</f>
-        <v>-20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
+        <v>20</v>
       </c>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
@@ -4248,14 +3732,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B60" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
       <c r="C60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4277,16 +3755,13 @@
         <v>1</v>
       </c>
       <c r="H60" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
-        <v>16</v>
-      </c>
-      <c r="I60" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="1"/>
       <c r="J60" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="K60" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4294,8 +3769,8 @@
       </c>
       <c r="L60" s="1"/>
       <c r="M60" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="2" t="str">
@@ -4303,8 +3778,8 @@
         <v/>
       </c>
       <c r="P60" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-9.0)</f>
-        <v>-9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
@@ -4315,14 +3790,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B61" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
       <c r="C61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4344,16 +3813,13 @@
         <v>1</v>
       </c>
       <c r="H61" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
-      </c>
-      <c r="I61" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="1"/>
       <c r="J61" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="K61" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4361,8 +3827,8 @@
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="2" t="str">
@@ -4370,8 +3836,8 @@
         <v/>
       </c>
       <c r="P61" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-17.0)</f>
-        <v>-17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),17.0)</f>
+        <v>17</v>
       </c>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
@@ -4382,14 +3848,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B62" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
       <c r="C62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4411,16 +3871,13 @@
         <v>1</v>
       </c>
       <c r="H62" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
-      </c>
-      <c r="I62" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="1"/>
       <c r="J62" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="K62" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4428,8 +3885,8 @@
       </c>
       <c r="L62" s="1"/>
       <c r="M62" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.25)</f>
+        <v>9.25</v>
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="2" t="str">
@@ -4437,8 +3894,8 @@
         <v/>
       </c>
       <c r="P62" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-12.0)</f>
-        <v>-12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
@@ -4449,14 +3906,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B63" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
-        <v>47</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
       <c r="C63" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4478,25 +3929,22 @@
         <v>1</v>
       </c>
       <c r="H63" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),47.0)</f>
-        <v>47</v>
-      </c>
-      <c r="I63" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="1"/>
       <c r="J63" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="K63" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L63" s="1"/>
       <c r="M63" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="2" t="str">
@@ -4504,8 +3952,8 @@
         <v/>
       </c>
       <c r="P63" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-38.0)</f>
-        <v>-38</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),66.0)</f>
+        <v>66</v>
       </c>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
@@ -4516,14 +3964,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B64" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
       <c r="C64" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4545,13 +3987,10 @@
         <v>1</v>
       </c>
       <c r="H64" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
-      </c>
-      <c r="I64" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="1"/>
       <c r="J64" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
@@ -4571,8 +4010,8 @@
         <v/>
       </c>
       <c r="P64" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-7.0)</f>
-        <v>-7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
@@ -4583,14 +4022,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B65" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
       <c r="C65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4612,16 +4045,13 @@
         <v>1</v>
       </c>
       <c r="H65" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
-      </c>
-      <c r="I65" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="1"/>
       <c r="J65" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="K65" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4629,8 +4059,8 @@
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="2" t="str">
@@ -4638,8 +4068,8 @@
         <v/>
       </c>
       <c r="P65" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-10.0)</f>
-        <v>-10</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),16.0)</f>
+        <v>16</v>
       </c>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
@@ -4650,14 +4080,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B66" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
       <c r="C66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4679,16 +4103,13 @@
         <v>1</v>
       </c>
       <c r="H66" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
-      </c>
-      <c r="I66" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="1"/>
       <c r="J66" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="K66" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4696,8 +4117,8 @@
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="2" t="str">
@@ -4705,8 +4126,8 @@
         <v/>
       </c>
       <c r="P66" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-14.0)</f>
-        <v>-14</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
       </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
@@ -4717,14 +4138,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B67" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
       <c r="C67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4746,25 +4161,22 @@
         <v>1</v>
       </c>
       <c r="H67" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
-        <v>52</v>
-      </c>
-      <c r="I67" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="1"/>
       <c r="J67" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
+        <v>64</v>
       </c>
       <c r="K67" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L67" s="1"/>
       <c r="M67" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
-        <v>19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
+        <v>64</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="2" t="str">
@@ -4772,8 +4184,8 @@
         <v/>
       </c>
       <c r="P67" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-33.0)</f>
-        <v>-33</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),64.0)</f>
+        <v>64</v>
       </c>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
@@ -4784,14 +4196,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B68" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
       <c r="C68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4813,13 +4219,10 @@
         <v>1</v>
       </c>
       <c r="H68" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
-      <c r="I68" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="1"/>
       <c r="J68" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -4839,8 +4242,8 @@
         <v/>
       </c>
       <c r="P68" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-7.0)</f>
-        <v>-7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
@@ -4851,14 +4254,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B69" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
-      </c>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
       <c r="C69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4880,16 +4277,13 @@
         <v>1</v>
       </c>
       <c r="H69" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),23.0)</f>
-        <v>23</v>
-      </c>
-      <c r="I69" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="1"/>
       <c r="J69" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="K69" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4897,8 +4291,8 @@
       </c>
       <c r="L69" s="1"/>
       <c r="M69" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="N69" s="1"/>
       <c r="O69" s="2" t="str">
@@ -4906,8 +4300,8 @@
         <v/>
       </c>
       <c r="P69" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-19.0)</f>
-        <v>-19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
@@ -4918,14 +4312,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B70" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
-      </c>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
       <c r="C70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -4947,16 +4335,13 @@
         <v>1</v>
       </c>
       <c r="H70" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
-        <v>35</v>
-      </c>
-      <c r="I70" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="1"/>
       <c r="J70" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="K70" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4964,8 +4349,8 @@
       </c>
       <c r="L70" s="1"/>
       <c r="M70" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="2" t="str">
@@ -4973,8 +4358,8 @@
         <v/>
       </c>
       <c r="P70" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-31.0)</f>
-        <v>-31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
@@ -4985,14 +4370,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B71" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
       <c r="C71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5014,25 +4393,22 @@
         <v>1</v>
       </c>
       <c r="H71" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
-      <c r="I71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
         <v>15</v>
       </c>
-      <c r="J71" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
       <c r="K71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L71" s="1"/>
+      <c r="M71" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
         <v>15</v>
-      </c>
-      <c r="L71" s="1"/>
-      <c r="M71" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
       </c>
       <c r="N71" s="1"/>
       <c r="O71" s="2" t="str">
@@ -5040,8 +4416,8 @@
         <v/>
       </c>
       <c r="P71" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-6.0)</f>
-        <v>-6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
@@ -5052,14 +4428,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B72" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
       <c r="C72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5081,16 +4451,13 @@
         <v>1</v>
       </c>
       <c r="H72" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
-      </c>
-      <c r="I72" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="1"/>
       <c r="J72" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="K72" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -5098,8 +4465,8 @@
       </c>
       <c r="L72" s="1"/>
       <c r="M72" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="2" t="str">
@@ -5107,8 +4474,8 @@
         <v/>
       </c>
       <c r="P72" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-19.0)</f>
-        <v>-19</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
+        <v>15</v>
       </c>
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
@@ -5119,14 +4486,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B73" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
       <c r="C73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5148,25 +4509,22 @@
         <v>12</v>
       </c>
       <c r="H73" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="J73" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
       <c r="K73" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),35.0)</f>
+        <v>35</v>
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="2" t="str">
@@ -5174,8 +4532,8 @@
         <v/>
       </c>
       <c r="P73" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
@@ -5186,15 +4544,12 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B74" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="C74" s="1"/>
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÃO DE BATATA E CIA")</f>
         <v>PÃO DE BATATA E CIA</v>
@@ -5212,16 +4567,13 @@
         <v>3</v>
       </c>
       <c r="H74" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I74" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="1"/>
       <c r="J74" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="K74" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -5229,8 +4581,8 @@
       </c>
       <c r="L74" s="1"/>
       <c r="M74" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),392.0)</f>
-        <v>392</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1128.0)</f>
+        <v>1128</v>
       </c>
       <c r="N74" s="1"/>
       <c r="O74" s="2" t="str">
@@ -5238,8 +4590,8 @@
         <v/>
       </c>
       <c r="P74" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q74" s="1"/>
       <c r="R74" s="2">
@@ -5253,15 +4605,12 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B75" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C75" s="1"/>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÃO DE BATATA E CIA")</f>
         <v>PÃO DE BATATA E CIA</v>
@@ -5279,25 +4628,22 @@
         <v>3</v>
       </c>
       <c r="H75" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I75" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="1"/>
       <c r="J75" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="K75" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L75" s="1"/>
       <c r="M75" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),140.0)</f>
-        <v>140</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),222.0)</f>
+        <v>222</v>
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="2" t="str">
@@ -5305,8 +4651,8 @@
         <v/>
       </c>
       <c r="P75" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q75" s="1"/>
       <c r="R75" s="2">
@@ -5320,17 +4666,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="B76" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C76" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÃO DE BATATA E CIA")</f>
@@ -5349,25 +4689,22 @@
         <v>3</v>
       </c>
       <c r="H76" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I76" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="1"/>
       <c r="J76" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
       <c r="K76" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L76" s="1"/>
       <c r="M76" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),38.0)</f>
+        <v>38</v>
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="2" t="str">
@@ -5375,8 +4712,8 @@
         <v/>
       </c>
       <c r="P76" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q76" s="1"/>
       <c r="R76" s="2">
@@ -5390,17 +4727,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B77" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C77" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PÃO DE BATATA E CIA")</f>
@@ -5419,25 +4750,22 @@
         <v>2</v>
       </c>
       <c r="H77" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I77" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="1"/>
       <c r="J77" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
       <c r="K77" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L77" s="1"/>
       <c r="M77" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
-        <v>25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),36.0)</f>
+        <v>36</v>
       </c>
       <c r="N77" s="1"/>
       <c r="O77" s="2" t="str">
@@ -5445,8 +4773,8 @@
         <v/>
       </c>
       <c r="P77" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q77" s="1"/>
       <c r="R77" s="2">
@@ -5460,14 +4788,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B78" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
       <c r="C78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5489,25 +4811,22 @@
         <v>4</v>
       </c>
       <c r="H78" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="I78" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J78" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
       <c r="K78" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L78" s="1"/>
       <c r="M78" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
       </c>
       <c r="N78" s="1"/>
       <c r="O78" s="2" t="str">
@@ -5515,8 +4834,8 @@
         <v/>
       </c>
       <c r="P78" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
@@ -5527,14 +4846,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B79" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
       <c r="C79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5556,25 +4869,22 @@
         <v>4</v>
       </c>
       <c r="H79" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I79" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="J79" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
       <c r="K79" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L79" s="1"/>
       <c r="M79" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
       </c>
       <c r="N79" s="1"/>
       <c r="O79" s="2" t="str">
@@ -5582,8 +4892,8 @@
         <v/>
       </c>
       <c r="P79" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
@@ -5594,15 +4904,12 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B80" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C80" s="1"/>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATELIE DOS SABORES - MÍN. 400,00")</f>
         <v>ATELIE DOS SABORES - MÍN. 400,00</v>
@@ -5620,13 +4927,10 @@
         <v>32</v>
       </c>
       <c r="H80" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I80" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I80" s="1"/>
       <c r="J80" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -5646,8 +4950,8 @@
         <v/>
       </c>
       <c r="P80" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
@@ -5658,17 +4962,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B81" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C81" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D81" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ATELIE DOS SABORES - MÍN. 400,00")</f>
@@ -5690,22 +4988,19 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I81" s="2">
+      <c r="I81" s="1"/>
+      <c r="J81" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="J81" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
       <c r="K81" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L81" s="1"/>
       <c r="M81" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),42.0)</f>
+        <v>42</v>
       </c>
       <c r="N81" s="1"/>
       <c r="O81" s="2" t="str">
@@ -5713,8 +5008,8 @@
         <v/>
       </c>
       <c r="P81" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
@@ -5725,14 +5020,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B82" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
       <c r="C82" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5754,13 +5043,10 @@
         <v>12</v>
       </c>
       <c r="H82" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I82" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I82" s="1"/>
       <c r="J82" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -5771,8 +5057,8 @@
       </c>
       <c r="L82" s="1"/>
       <c r="M82" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),14.0)</f>
+        <v>14</v>
       </c>
       <c r="N82" s="1"/>
       <c r="O82" s="2" t="str">
@@ -5780,8 +5066,8 @@
         <v/>
       </c>
       <c r="P82" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
@@ -5792,14 +5078,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B83" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
       <c r="C83" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5821,16 +5101,13 @@
         <v>1</v>
       </c>
       <c r="H83" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I83" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="1"/>
       <c r="J83" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="K83" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -5838,8 +5115,8 @@
       </c>
       <c r="L83" s="1"/>
       <c r="M83" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),20.0)</f>
-        <v>20</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),52.0)</f>
+        <v>52</v>
       </c>
       <c r="N83" s="1"/>
       <c r="O83" s="2" t="str">
@@ -5847,8 +5124,8 @@
         <v/>
       </c>
       <c r="P83" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="Q83" s="1"/>
       <c r="R83" s="2">
@@ -5862,14 +5139,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B84" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
       <c r="C84" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5891,16 +5162,13 @@
         <v>1</v>
       </c>
       <c r="H84" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I84" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="1"/>
       <c r="J84" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K84" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -5908,8 +5176,8 @@
       </c>
       <c r="L84" s="1"/>
       <c r="M84" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),18.0)</f>
-        <v>18</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),29.0)</f>
+        <v>29</v>
       </c>
       <c r="N84" s="1"/>
       <c r="O84" s="2" t="str">
@@ -5917,8 +5185,8 @@
         <v/>
       </c>
       <c r="P84" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q84" s="1"/>
       <c r="R84" s="2">
@@ -5932,14 +5200,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B85" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
       <c r="C85" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -5961,13 +5223,10 @@
         <v>3.5</v>
       </c>
       <c r="H85" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I85" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="1"/>
       <c r="J85" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -5987,8 +5246,8 @@
         <v/>
       </c>
       <c r="P85" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
@@ -5999,14 +5258,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B86" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
       <c r="C86" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6028,25 +5281,22 @@
         <v>1.5</v>
       </c>
       <c r="H86" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="I86" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="J86" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
       <c r="K86" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="L86" s="1"/>
       <c r="M86" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.62)</f>
-        <v>0.62</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.72)</f>
+        <v>1.72</v>
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="2" t="str">
@@ -6054,8 +5304,8 @@
         <v/>
       </c>
       <c r="P86" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
@@ -6066,14 +5316,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B87" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
       <c r="C87" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6095,13 +5339,10 @@
         <v>10</v>
       </c>
       <c r="H87" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I87" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I87" s="1"/>
       <c r="J87" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -6112,8 +5353,8 @@
       </c>
       <c r="L87" s="1"/>
       <c r="M87" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.03)</f>
-        <v>10.03</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.638)</f>
+        <v>11.638</v>
       </c>
       <c r="N87" s="1"/>
       <c r="O87" s="2" t="str">
@@ -6121,8 +5362,8 @@
         <v/>
       </c>
       <c r="P87" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
@@ -6133,14 +5374,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B88" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
       <c r="C88" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6162,25 +5397,22 @@
         <v>1</v>
       </c>
       <c r="H88" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I88" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I88" s="1"/>
       <c r="J88" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
       <c r="K88" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L88" s="1"/>
       <c r="M88" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.778)</f>
-        <v>2.778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.149)</f>
+        <v>3.149</v>
       </c>
       <c r="N88" s="1"/>
       <c r="O88" s="2" t="str">
@@ -6188,8 +5420,8 @@
         <v/>
       </c>
       <c r="P88" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
@@ -6200,14 +5432,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B89" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
       <c r="C89" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6229,13 +5455,10 @@
         <v>5</v>
       </c>
       <c r="H89" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I89" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I89" s="1"/>
       <c r="J89" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6246,8 +5469,8 @@
       </c>
       <c r="L89" s="1"/>
       <c r="M89" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.005)</f>
+        <v>1.005</v>
       </c>
       <c r="N89" s="1"/>
       <c r="O89" s="2" t="str">
@@ -6255,8 +5478,8 @@
         <v/>
       </c>
       <c r="P89" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
@@ -6267,14 +5490,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B90" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
       <c r="C90" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6296,13 +5513,10 @@
         <v>996</v>
       </c>
       <c r="H90" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I90" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I90" s="1"/>
       <c r="J90" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6322,8 +5536,8 @@
         <v/>
       </c>
       <c r="P90" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
@@ -6334,14 +5548,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B91" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
       <c r="C91" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6363,13 +5571,10 @@
         <v>1000</v>
       </c>
       <c r="H91" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I91" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I91" s="1"/>
       <c r="J91" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6389,8 +5594,8 @@
         <v/>
       </c>
       <c r="P91" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
@@ -6401,14 +5606,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B92" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
       <c r="C92" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6430,13 +5629,10 @@
         <v>1000</v>
       </c>
       <c r="H92" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I92" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I92" s="1"/>
       <c r="J92" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6456,8 +5652,8 @@
         <v/>
       </c>
       <c r="P92" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
@@ -6468,14 +5664,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B93" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
       <c r="C93" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6500,17 +5690,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I93" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="I93" s="1"/>
       <c r="J93" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K93" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L93" s="1"/>
       <c r="M93" s="3" t="str">
@@ -6535,14 +5722,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B94" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
       <c r="C94" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6564,13 +5745,10 @@
         <v>0.75</v>
       </c>
       <c r="H94" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I94" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="1"/>
       <c r="J94" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -6581,8 +5759,8 @@
       </c>
       <c r="L94" s="1"/>
       <c r="M94" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.43)</f>
-        <v>0.43</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.91)</f>
+        <v>0.91</v>
       </c>
       <c r="N94" s="1"/>
       <c r="O94" s="2" t="str">
@@ -6590,8 +5768,8 @@
         <v/>
       </c>
       <c r="P94" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
@@ -6602,14 +5780,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B95" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
       <c r="C95" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6631,13 +5803,10 @@
         <v>0.75</v>
       </c>
       <c r="H95" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I95" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I95" s="1"/>
       <c r="J95" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6648,8 +5817,8 @@
       </c>
       <c r="L95" s="1"/>
       <c r="M95" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.25)</f>
-        <v>0.25</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.37)</f>
+        <v>0.37</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="2" t="str">
@@ -6657,8 +5826,8 @@
         <v/>
       </c>
       <c r="P95" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
@@ -6669,14 +5838,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B96" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
       <c r="C96" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6698,16 +5861,13 @@
         <v>0.75</v>
       </c>
       <c r="H96" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I96" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I96" s="1"/>
       <c r="J96" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="K96" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -6715,8 +5875,8 @@
       </c>
       <c r="L96" s="1"/>
       <c r="M96" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.17)</f>
-        <v>0.17</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.59)</f>
+        <v>0.59</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="2" t="str">
@@ -6724,8 +5884,8 @@
         <v/>
       </c>
       <c r="P96" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
@@ -6736,15 +5896,12 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B97" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C97" s="1"/>
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D97" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIO QUALITY")</f>
         <v>RIO QUALITY</v>
@@ -6762,13 +5919,10 @@
         <v>12</v>
       </c>
       <c r="H97" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I97" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="1"/>
       <c r="J97" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6788,8 +5942,8 @@
         <v/>
       </c>
       <c r="P97" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
@@ -6800,15 +5954,12 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B98" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C98" s="1"/>
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D98" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OPIPARO")</f>
         <v>OPIPARO</v>
@@ -6826,25 +5977,22 @@
         <v>1</v>
       </c>
       <c r="H98" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I98" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I98" s="1"/>
       <c r="J98" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K98" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L98" s="1"/>
       <c r="M98" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.54)</f>
-        <v>0.54</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.07)</f>
+        <v>2.07</v>
       </c>
       <c r="N98" s="1"/>
       <c r="O98" s="2" t="str">
@@ -6852,8 +6000,8 @@
         <v/>
       </c>
       <c r="P98" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
@@ -6864,14 +6012,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B99" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
       <c r="C99" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -6893,25 +6035,22 @@
         <v>1</v>
       </c>
       <c r="H99" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I99" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I99" s="1"/>
       <c r="J99" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K99" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L99" s="1"/>
       <c r="M99" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.12)</f>
-        <v>1.12</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.24)</f>
+        <v>2.24</v>
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="2" t="str">
@@ -6919,8 +6058,8 @@
         <v/>
       </c>
       <c r="P99" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
@@ -6931,15 +6070,12 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B100" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C100" s="1"/>
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D100" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OPIPARO")</f>
         <v>OPIPARO</v>
@@ -6957,16 +6093,13 @@
         <v>1</v>
       </c>
       <c r="H100" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I100" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I100" s="1"/>
       <c r="J100" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K100" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -6974,8 +6107,8 @@
       </c>
       <c r="L100" s="1"/>
       <c r="M100" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
-        <v>0.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="N100" s="1"/>
       <c r="O100" s="2" t="str">
@@ -6983,8 +6116,8 @@
         <v/>
       </c>
       <c r="P100" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
@@ -6995,14 +6128,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="B101" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
       <c r="C101" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7024,13 +6151,10 @@
         <v>1</v>
       </c>
       <c r="H101" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I101" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I101" s="1"/>
       <c r="J101" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -7050,8 +6174,8 @@
         <v/>
       </c>
       <c r="P101" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
@@ -7062,15 +6186,12 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B102" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="C102" s="1"/>
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="D102" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OPIPARO")</f>
         <v>OPIPARO</v>
@@ -7088,13 +6209,10 @@
         <v>1.2</v>
       </c>
       <c r="H102" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I102" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I102" s="1"/>
       <c r="J102" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -7105,8 +6223,8 @@
       </c>
       <c r="L102" s="1"/>
       <c r="M102" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.31)</f>
-        <v>0.31</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
+        <v>0.4</v>
       </c>
       <c r="N102" s="1"/>
       <c r="O102" s="2" t="str">
@@ -7114,8 +6232,8 @@
         <v/>
       </c>
       <c r="P102" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
@@ -7126,14 +6244,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B103" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
       <c r="C103" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7155,25 +6267,22 @@
         <v>6</v>
       </c>
       <c r="H103" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I103" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I103" s="1"/>
       <c r="J103" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="K103" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L103" s="1"/>
-      <c r="M103" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.7)</f>
-        <v>7.7</v>
+      <c r="M103" s="3" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
+        <v/>
       </c>
       <c r="N103" s="1"/>
       <c r="O103" s="2" t="str">
@@ -7181,8 +6290,8 @@
         <v/>
       </c>
       <c r="P103" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
@@ -7193,14 +6302,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B104" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
       <c r="C104" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7222,25 +6325,22 @@
         <v>10</v>
       </c>
       <c r="H104" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I104" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="1"/>
       <c r="J104" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
       <c r="K104" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L104" s="1"/>
       <c r="M104" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),32.0)</f>
+        <v>32</v>
       </c>
       <c r="N104" s="1"/>
       <c r="O104" s="2" t="str">
@@ -7248,8 +6348,8 @@
         <v/>
       </c>
       <c r="P104" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
@@ -7260,14 +6360,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B105" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
       <c r="C105" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7289,25 +6383,22 @@
         <v>10</v>
       </c>
       <c r="H105" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I105" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="1"/>
       <c r="J105" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="K105" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L105" s="1"/>
       <c r="M105" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
-        <v>22</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),49.0)</f>
+        <v>49</v>
       </c>
       <c r="N105" s="1"/>
       <c r="O105" s="2" t="str">
@@ -7315,8 +6406,8 @@
         <v/>
       </c>
       <c r="P105" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
@@ -7327,14 +6418,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B106" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
       <c r="C106" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7356,16 +6441,13 @@
         <v>10</v>
       </c>
       <c r="H106" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="I106" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I106" s="1"/>
       <c r="J106" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K106" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -7373,8 +6455,8 @@
       </c>
       <c r="L106" s="1"/>
       <c r="M106" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),11.0)</f>
-        <v>11</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="N106" s="1"/>
       <c r="O106" s="2" t="str">
@@ -7382,8 +6464,8 @@
         <v/>
       </c>
       <c r="P106" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
@@ -7394,14 +6476,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B107" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
       <c r="C107" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7423,25 +6499,22 @@
         <v>10</v>
       </c>
       <c r="H107" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I107" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I107" s="1"/>
       <c r="J107" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K107" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L107" s="1"/>
       <c r="M107" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
-        <v>26</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="N107" s="1"/>
       <c r="O107" s="2" t="str">
@@ -7449,8 +6522,8 @@
         <v/>
       </c>
       <c r="P107" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
@@ -7461,14 +6534,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B108" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
-      </c>
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
       <c r="C108" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7490,16 +6557,13 @@
         <v>12</v>
       </c>
       <c r="H108" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
-      </c>
-      <c r="I108" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I108" s="1"/>
       <c r="J108" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="K108" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -7507,8 +6571,8 @@
       </c>
       <c r="L108" s="1"/>
       <c r="M108" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55.015)</f>
-        <v>55.015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),90.055)</f>
+        <v>90.055</v>
       </c>
       <c r="N108" s="1"/>
       <c r="O108" s="2" t="str">
@@ -7516,8 +6580,8 @@
         <v/>
       </c>
       <c r="P108" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
+        <v>8</v>
       </c>
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
@@ -7528,17 +6592,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B109" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="C109" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NAVEIA")</f>
@@ -7560,13 +6618,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I109" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I109" s="1"/>
       <c r="J109" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="K109" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -7574,8 +6629,8 @@
       </c>
       <c r="L109" s="1"/>
       <c r="M109" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.68)</f>
-        <v>3.68</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.435)</f>
+        <v>6.435</v>
       </c>
       <c r="N109" s="1"/>
       <c r="O109" s="2" t="str">
@@ -7583,8 +6638,8 @@
         <v/>
       </c>
       <c r="P109" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
@@ -7595,14 +6650,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
-      </c>
-      <c r="B110" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
       <c r="C110" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7624,25 +6673,22 @@
         <v>12</v>
       </c>
       <c r="H110" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
-      </c>
-      <c r="I110" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I110" s="1"/>
       <c r="J110" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="K110" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
-        <v>8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),100.0)</f>
-        <v>100</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),252.0)</f>
+        <v>252</v>
       </c>
       <c r="N110" s="1"/>
       <c r="O110" s="2" t="str">
@@ -7650,8 +6696,8 @@
         <v/>
       </c>
       <c r="P110" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),21.0)</f>
+        <v>21</v>
       </c>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
@@ -7662,14 +6708,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),10.0)</f>
-        <v>10</v>
-      </c>
-      <c r="B111" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
       <c r="C111" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7691,25 +6731,22 @@
         <v>12</v>
       </c>
       <c r="H111" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
-        <v>12</v>
-      </c>
-      <c r="I111" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I111" s="1"/>
       <c r="J111" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="K111" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L111" s="1"/>
       <c r="M111" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),108.0)</f>
-        <v>108</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),224.0)</f>
+        <v>224</v>
       </c>
       <c r="N111" s="1"/>
       <c r="O111" s="2" t="str">
@@ -7717,8 +6754,8 @@
         <v/>
       </c>
       <c r="P111" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),19.0)</f>
+        <v>19</v>
       </c>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
@@ -7729,14 +6766,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B112" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
       <c r="C112" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7758,25 +6789,22 @@
         <v>12</v>
       </c>
       <c r="H112" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I112" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I112" s="1"/>
       <c r="J112" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="K112" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L112" s="1"/>
       <c r="M112" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.6)</f>
+        <v>6.6</v>
       </c>
       <c r="N112" s="1"/>
       <c r="O112" s="2" t="str">
@@ -7784,8 +6812,8 @@
         <v/>
       </c>
       <c r="P112" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q112" s="1"/>
       <c r="R112" s="2">
@@ -7799,14 +6827,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B113" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
       <c r="C113" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7828,13 +6850,10 @@
         <v>12</v>
       </c>
       <c r="H113" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I113" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="1"/>
       <c r="J113" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -7854,8 +6873,8 @@
         <v/>
       </c>
       <c r="P113" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
@@ -7866,14 +6885,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B114" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
-      </c>
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
       <c r="C114" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7895,20 +6908,17 @@
         <v>1</v>
       </c>
       <c r="H114" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
-      </c>
-      <c r="I114" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I114" s="1"/>
       <c r="J114" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K114" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),30.0)</f>
-        <v>30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L114" s="1"/>
       <c r="M114" s="3" t="str">
@@ -7921,8 +6931,8 @@
         <v/>
       </c>
       <c r="P114" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-30.0)</f>
-        <v>-30</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
@@ -7933,14 +6943,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B115" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
       <c r="C115" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -7962,13 +6966,10 @@
         <v>50</v>
       </c>
       <c r="H115" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="I115" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I115" s="1"/>
       <c r="J115" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -7988,8 +6989,8 @@
         <v/>
       </c>
       <c r="P115" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-4.0)</f>
-        <v>-4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
@@ -8000,14 +7001,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B116" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
       <c r="C116" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8029,13 +7024,10 @@
         <v>50</v>
       </c>
       <c r="H116" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I116" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I116" s="1"/>
       <c r="J116" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8055,8 +7047,8 @@
         <v/>
       </c>
       <c r="P116" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
@@ -8067,14 +7059,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B117" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
       <c r="C117" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8096,13 +7082,10 @@
         <v>50</v>
       </c>
       <c r="H117" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
-      <c r="I117" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I117" s="1"/>
       <c r="J117" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8122,8 +7105,8 @@
         <v/>
       </c>
       <c r="P117" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-3.0)</f>
-        <v>-3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
@@ -8134,14 +7117,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B118" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
       <c r="C118" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8163,13 +7140,10 @@
         <v>500</v>
       </c>
       <c r="H118" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I118" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I118" s="1"/>
       <c r="J118" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8189,8 +7163,8 @@
         <v/>
       </c>
       <c r="P118" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
@@ -8201,14 +7175,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B119" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
       <c r="C119" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8230,20 +7198,17 @@
         <v>100</v>
       </c>
       <c r="H119" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I119" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I119" s="1"/>
       <c r="J119" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K119" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L119" s="1"/>
       <c r="M119" s="3" t="str">
@@ -8256,8 +7221,8 @@
         <v/>
       </c>
       <c r="P119" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
@@ -8268,14 +7233,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B120" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
       <c r="C120" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8297,20 +7256,17 @@
         <v>100</v>
       </c>
       <c r="H120" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I120" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I120" s="1"/>
       <c r="J120" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K120" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="3" t="str">
@@ -8323,8 +7279,8 @@
         <v/>
       </c>
       <c r="P120" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
@@ -8335,14 +7291,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B121" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
       <c r="C121" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8364,13 +7314,10 @@
         <v>100</v>
       </c>
       <c r="H121" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I121" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I121" s="1"/>
       <c r="J121" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8390,8 +7337,8 @@
         <v/>
       </c>
       <c r="P121" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
@@ -8402,14 +7349,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B122" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
       <c r="C122" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8431,13 +7372,10 @@
         <v>200</v>
       </c>
       <c r="H122" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I122" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I122" s="1"/>
       <c r="J122" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8457,8 +7395,8 @@
         <v/>
       </c>
       <c r="P122" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
@@ -8469,14 +7407,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B123" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
       <c r="C123" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8498,13 +7430,10 @@
         <v>1</v>
       </c>
       <c r="H123" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I123" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I123" s="1"/>
       <c r="J123" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8524,8 +7453,8 @@
         <v/>
       </c>
       <c r="P123" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
@@ -8536,14 +7465,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B124" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
       <c r="C124" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8568,17 +7491,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I124" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
-      </c>
+      <c r="I124" s="1"/>
       <c r="J124" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K124" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),15.0)</f>
-        <v>15</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L124" s="1"/>
       <c r="M124" s="3" t="str">
@@ -8603,14 +7523,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B125" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
       <c r="C125" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8635,17 +7549,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I125" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="I125" s="1"/>
       <c r="J125" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K125" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="3" t="str">
@@ -8670,14 +7581,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B126" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
       <c r="C126" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8699,13 +7604,10 @@
         <v>1</v>
       </c>
       <c r="H126" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I126" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I126" s="1"/>
       <c r="J126" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8725,8 +7627,8 @@
         <v/>
       </c>
       <c r="P126" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
@@ -8737,14 +7639,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B127" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
       <c r="C127" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8766,13 +7662,10 @@
         <v>1</v>
       </c>
       <c r="H127" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I127" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I127" s="1"/>
       <c r="J127" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8792,8 +7685,8 @@
         <v/>
       </c>
       <c r="P127" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
@@ -8804,14 +7697,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B128" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
       <c r="C128" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8833,13 +7720,10 @@
         <v>100</v>
       </c>
       <c r="H128" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I128" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I128" s="1"/>
       <c r="J128" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8859,8 +7743,8 @@
         <v/>
       </c>
       <c r="P128" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
@@ -8871,14 +7755,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B129" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
       <c r="C129" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8900,13 +7778,10 @@
         <v>1</v>
       </c>
       <c r="H129" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I129" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I129" s="1"/>
       <c r="J129" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8926,8 +7801,8 @@
         <v/>
       </c>
       <c r="P129" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
@@ -8938,14 +7813,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B130" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A130" s="1"/>
+      <c r="B130" s="1"/>
       <c r="C130" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -8967,13 +7836,10 @@
         <v>1</v>
       </c>
       <c r="H130" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I130" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I130" s="1"/>
       <c r="J130" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -8993,8 +7859,8 @@
         <v/>
       </c>
       <c r="P130" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
@@ -9005,14 +7871,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B131" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
       <c r="C131" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9034,13 +7894,10 @@
         <v>1</v>
       </c>
       <c r="H131" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I131" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I131" s="1"/>
       <c r="J131" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9060,8 +7917,8 @@
         <v/>
       </c>
       <c r="P131" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
@@ -9072,14 +7929,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B132" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
       <c r="C132" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9101,13 +7952,10 @@
         <v>1</v>
       </c>
       <c r="H132" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I132" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I132" s="1"/>
       <c r="J132" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9127,8 +7975,8 @@
         <v/>
       </c>
       <c r="P132" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
@@ -9139,14 +7987,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B133" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
+      <c r="A133" s="1"/>
+      <c r="B133" s="1"/>
       <c r="C133" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9168,13 +8010,10 @@
         <v>4</v>
       </c>
       <c r="H133" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="I133" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I133" s="1"/>
       <c r="J133" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9194,8 +8033,8 @@
         <v/>
       </c>
       <c r="P133" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-5.0)</f>
-        <v>-5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
@@ -9206,14 +8045,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B134" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
       <c r="C134" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9235,20 +8068,17 @@
         <v>5</v>
       </c>
       <c r="H134" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I134" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I134" s="1"/>
       <c r="J134" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K134" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L134" s="1"/>
       <c r="M134" s="3" t="str">
@@ -9261,8 +8091,8 @@
         <v/>
       </c>
       <c r="P134" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
@@ -9273,14 +8103,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B135" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A135" s="1"/>
+      <c r="B135" s="1"/>
       <c r="C135" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9305,10 +8129,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I135" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I135" s="1"/>
       <c r="J135" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9340,14 +8161,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B136" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
       <c r="C136" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9369,20 +8184,17 @@
         <v>1000</v>
       </c>
       <c r="H136" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
-      <c r="I136" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I136" s="1"/>
       <c r="J136" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K136" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L136" s="1"/>
       <c r="M136" s="3" t="str">
@@ -9395,8 +8207,8 @@
         <v/>
       </c>
       <c r="P136" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-6.0)</f>
-        <v>-6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
@@ -9407,14 +8219,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B137" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A137" s="1"/>
+      <c r="B137" s="1"/>
       <c r="C137" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9439,17 +8245,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I137" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="I137" s="1"/>
       <c r="J137" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="K137" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="L137" s="1"/>
       <c r="M137" s="3" t="str">
@@ -9474,14 +8277,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B138" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
       <c r="C138" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9503,13 +8300,10 @@
         <v>5</v>
       </c>
       <c r="H138" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I138" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I138" s="1"/>
       <c r="J138" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9529,8 +8323,8 @@
         <v/>
       </c>
       <c r="P138" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
@@ -9541,14 +8335,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B139" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
-      </c>
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
       <c r="C139" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9570,13 +8358,10 @@
         <v>-</v>
       </c>
       <c r="H139" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
-        <v>13</v>
-      </c>
-      <c r="I139" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I139" s="1"/>
       <c r="J139" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9596,8 +8381,8 @@
         <v/>
       </c>
       <c r="P139" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-13.0)</f>
-        <v>-13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
@@ -9608,14 +8393,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B140" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
       <c r="C140" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9637,13 +8416,10 @@
         <v>1</v>
       </c>
       <c r="H140" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
-      <c r="I140" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I140" s="1"/>
       <c r="J140" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9663,8 +8439,8 @@
         <v/>
       </c>
       <c r="P140" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-6.0)</f>
-        <v>-6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
@@ -9675,14 +8451,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B141" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="A141" s="1"/>
+      <c r="B141" s="1"/>
       <c r="C141" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9704,13 +8474,10 @@
         <v>30</v>
       </c>
       <c r="H141" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="I141" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I141" s="1"/>
       <c r="J141" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9730,8 +8497,8 @@
         <v/>
       </c>
       <c r="P141" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
@@ -9742,14 +8509,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B142" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
       <c r="C142" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9768,13 +8529,10 @@
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="I142" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I142" s="1"/>
       <c r="J142" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9794,8 +8552,8 @@
         <v/>
       </c>
       <c r="P142" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-2.0)</f>
-        <v>-2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
@@ -9806,14 +8564,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B143" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A143" s="1"/>
+      <c r="B143" s="1"/>
       <c r="C143" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9835,10 +8587,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I143" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I143" s="1"/>
       <c r="J143" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9870,14 +8619,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B144" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A144" s="1"/>
+      <c r="B144" s="1"/>
       <c r="C144" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9896,10 +8639,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I144" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I144" s="1"/>
       <c r="J144" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9931,14 +8671,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B145" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A145" s="1"/>
+      <c r="B145" s="1"/>
       <c r="C145" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -9963,10 +8697,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I145" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I145" s="1"/>
       <c r="J145" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -9998,14 +8729,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B146" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A146" s="1"/>
+      <c r="B146" s="1"/>
       <c r="C146" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10030,10 +8755,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I146" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I146" s="1"/>
       <c r="J146" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -10065,14 +8787,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B147" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A147" s="1"/>
+      <c r="B147" s="1"/>
       <c r="C147" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10097,10 +8813,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I147" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I147" s="1"/>
       <c r="J147" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -10132,14 +8845,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B148" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A148" s="1"/>
+      <c r="B148" s="1"/>
       <c r="C148" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10164,10 +8871,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I148" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I148" s="1"/>
       <c r="J148" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -10199,14 +8903,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B149" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
       <c r="C149" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10231,13 +8929,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I149" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I149" s="1"/>
       <c r="J149" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="K149" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -10245,8 +8940,8 @@
       </c>
       <c r="L149" s="1"/>
       <c r="M149" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.187)</f>
-        <v>0.187</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.114)</f>
+        <v>4.114</v>
       </c>
       <c r="N149" s="1"/>
       <c r="O149" s="2" t="str">
@@ -10254,8 +8949,8 @@
         <v/>
       </c>
       <c r="P149" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),22.0)</f>
+        <v>22</v>
       </c>
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
@@ -10266,14 +8961,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B150" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A150" s="1"/>
+      <c r="B150" s="1"/>
       <c r="C150" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10298,10 +8987,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I150" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I150" s="1"/>
       <c r="J150" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -10333,14 +9019,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B151" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A151" s="1"/>
+      <c r="B151" s="1"/>
       <c r="C151" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10365,13 +9045,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I151" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I151" s="1"/>
       <c r="J151" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="K151" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -10379,8 +9056,8 @@
       </c>
       <c r="L151" s="1"/>
       <c r="M151" s="3">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.187)</f>
-        <v>0.187</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.431)</f>
+        <v>2.431</v>
       </c>
       <c r="N151" s="1"/>
       <c r="O151" s="2" t="str">
@@ -10388,8 +9065,8 @@
         <v/>
       </c>
       <c r="P151" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),13.0)</f>
+        <v>13</v>
       </c>
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
@@ -10400,14 +9077,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B152" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
       <c r="C152" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10420,10 +9091,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I152" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I152" s="1"/>
       <c r="J152" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -10455,14 +9123,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="B153" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
       <c r="C153" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
         <v>-</v>
@@ -10475,10 +9137,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I153" s="2">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="I153" s="1"/>
       <c r="J153" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
